--- a/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
@@ -1,203 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utilisateur/kDrive/Claude_Travail/livrables/documents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2669E6B-021D-9343-9437-960105C38A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="2520" windowWidth="28040" windowHeight="17440" xr2:uid="{806A7FE3-5762-434F-B27C-12A55658559F}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6460" yWindow="2520" windowWidth="28040" windowHeight="17440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
-  <si>
-    <t>Tes 13 jobs</t>
-  </si>
-  <si>
-    <t>Jour</t>
-  </si>
-  <si>
-    <t>Heure</t>
-  </si>
-  <si>
-    <t>Job</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Dimanche</t>
-  </si>
-  <si>
-    <t>7h03</t>
-  </si>
-  <si>
-    <t>revenus-passifs-lecon</t>
-  </si>
-  <si>
-    <t>Leçon — parcours 10</t>
-  </si>
-  <si>
-    <t>8h03</t>
-  </si>
-  <si>
-    <t>imac-veille</t>
-  </si>
-  <si>
-    <t>Veille</t>
-  </si>
-  <si>
-    <t>11h03</t>
-  </si>
-  <si>
-    <t>controle-livrables</t>
-  </si>
-  <si>
-    <t>Contrôle qualité</t>
-  </si>
-  <si>
-    <t>Lundi</t>
-  </si>
-  <si>
-    <t>psychopathologie-lecon</t>
-  </si>
-  <si>
-    <t>Leçon</t>
-  </si>
-  <si>
-    <t>8h30</t>
-  </si>
-  <si>
-    <t>rbpp-pipeline</t>
-  </si>
-  <si>
-    <t>Veille HAS + quiz + infographies</t>
-  </si>
-  <si>
-    <t>Mardi</t>
-  </si>
-  <si>
-    <t>dzogchen-lecon</t>
-  </si>
-  <si>
-    <t>9h03</t>
-  </si>
-  <si>
-    <t>hypnose-lecon</t>
-  </si>
-  <si>
-    <t>Mercredi</t>
-  </si>
-  <si>
-    <t>serafin-ph-veille</t>
-  </si>
-  <si>
-    <t>enneagramme-lecon</t>
-  </si>
-  <si>
-    <t>Jeudi</t>
-  </si>
-  <si>
-    <t>stoicisme-lecon</t>
-  </si>
-  <si>
-    <t>9h33</t>
-  </si>
-  <si>
-    <t>entretien-motivationnel-lecon</t>
-  </si>
-  <si>
-    <t>Vendredi</t>
-  </si>
-  <si>
-    <t>appli-ia-lecon</t>
-  </si>
-  <si>
-    <t>Leçon — parcours 12</t>
-  </si>
-  <si>
-    <t>Samedi</t>
-  </si>
-  <si>
-    <t>placement-financier-lecon</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="13.7"/>
       <name val="Helvetica"/>
       <family val="2"/>
+      <sz val="13.7"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Helvetica"/>
       <family val="2"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Helvetica"/>
       <family val="2"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="13"/>
       <name val="Courier New"/>
       <family val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -230,27 +93,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -570,205 +492,311 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DF4FE5-981B-4243-A3FC-E6635A94280F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col width="13.83203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="40.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="30.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>17</v>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tes 13 jobs</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Jour</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Heure</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>7h03</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>revenus-passifs-lecon</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>imac-veille</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Veille</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>11h03</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>controle-livrables</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Contrôle qualité</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Lundi</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>psychopathologie-lecon</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Leçon</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>8h30</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>rbpp-pipeline</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Veille HAS + quiz + infographies</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Mardi</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>dzogchen-lecon</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Leçon</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>9h03</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>hypnose-lecon</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Leçon</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Mercredi</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>serafin-ph-veille</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Veille</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>9h03</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>enneagramme-lecon</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Leçon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Jeudi</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>stoicisme-lecon</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Leçon</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>9h33</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>astrologie-karmique-lecon</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>appli-ia-lecon</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>placement-financier-lecon</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Leçon</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
@@ -73,7 +73,7 @@
     <t>psychopathologie-lecon</t>
   </si>
   <si>
-    <t>Leçon</t>
+    <t>Leçon — parcours 20</t>
   </si>
   <si>
     <t>8h30</t>

--- a/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
@@ -1,187 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utilisateur/kDrive/Claude_Travail/livrables/documents/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E0FEBE-BD8D-9146-85E7-437EA4820BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="2520" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6460" yWindow="2520" windowWidth="28040" windowHeight="17440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuil1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
-  <si>
-    <t>Tes 13 jobs</t>
-  </si>
-  <si>
-    <t>Jour</t>
-  </si>
-  <si>
-    <t>Heure</t>
-  </si>
-  <si>
-    <t>Job</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Dimanche</t>
-  </si>
-  <si>
-    <t>7h03</t>
-  </si>
-  <si>
-    <t>revenus-passifs-lecon</t>
-  </si>
-  <si>
-    <t>Leçon — parcours 10</t>
-  </si>
-  <si>
-    <t>8h03</t>
-  </si>
-  <si>
-    <t>imac-veille</t>
-  </si>
-  <si>
-    <t>Veille</t>
-  </si>
-  <si>
-    <t>11h03</t>
-  </si>
-  <si>
-    <t>controle-livrables</t>
-  </si>
-  <si>
-    <t>Contrôle qualité</t>
-  </si>
-  <si>
-    <t>Lundi</t>
-  </si>
-  <si>
-    <t>psychopathologie-lecon</t>
-  </si>
-  <si>
-    <t>Leçon — parcours 20</t>
-  </si>
-  <si>
-    <t>8h30</t>
-  </si>
-  <si>
-    <t>rbpp-pipeline</t>
-  </si>
-  <si>
-    <t>Veille HAS + quiz + infographies</t>
-  </si>
-  <si>
-    <t>Mardi</t>
-  </si>
-  <si>
-    <t>dzogchen-lecon</t>
-  </si>
-  <si>
-    <t>9h03</t>
-  </si>
-  <si>
-    <t>hypnose-lecon</t>
-  </si>
-  <si>
-    <t>Mercredi</t>
-  </si>
-  <si>
-    <t>serafin-ph-veille</t>
-  </si>
-  <si>
-    <t>enneagramme-lecon</t>
-  </si>
-  <si>
-    <t>Jeudi</t>
-  </si>
-  <si>
-    <t>stoicisme-lecon</t>
-  </si>
-  <si>
-    <t>9h33</t>
-  </si>
-  <si>
-    <t>astrologie-karmique-lecon</t>
-  </si>
-  <si>
-    <t>Leçon — parcours 12</t>
-  </si>
-  <si>
-    <t>Vendredi</t>
-  </si>
-  <si>
-    <t>appli-ia-lecon</t>
-  </si>
-  <si>
-    <t>Samedi</t>
-  </si>
-  <si>
-    <t>placement-financier-lecon</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="13.7"/>
       <name val="Helvetica"/>
       <family val="2"/>
+      <sz val="13.7"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Helvetica"/>
       <family val="2"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Helvetica"/>
       <family val="2"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="13"/>
       <name val="Courier New"/>
       <family val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -214,27 +93,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -554,205 +492,382 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col width="13.83203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="40.6640625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="30.33203125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>17</v>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tes 13 jobs</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Jour</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Heure</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Numéro de la dernière leçon</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Dimanche</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>7h03</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>revenus-passifs-lecon</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 10</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>imac-veille</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Veille</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>11h03</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>controle-livrables</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Contrôle qualité</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Lundi</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>psychopathologie-lecon</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>8h30</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>rbpp-pipeline</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Veille HAS + quiz + infographies</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Mardi</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>dzogchen-lecon</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>9h03</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>hypnose-lecon</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Mercredi</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>serafin-ph-veille</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Veille</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>9h03</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>enneagramme-lecon</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Jeudi</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>stoicisme-lecon</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>9h33</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>astrologie-karmique-lecon</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 12</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>appli-ia-lecon</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 12</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Samedi</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>8h03</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>placement-financier-lecon</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Leçon — parcours 20</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
@@ -839,7 +839,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
@@ -866,7 +866,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="13.83203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -509,7 +509,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tes 13 jobs</t>
+          <t>Tes 14 jobs</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -844,27 +844,50 @@
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>9h03</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>ai-act-veille</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Veille — réglementaire</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Samedi</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>8h03</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>placement-financier-lecon</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Leçon — parcours 20</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>

--- a/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>

--- a/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
+++ b/livrables/documents/2026-08-09_Les 13 Jobs.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
